--- a/artfynd/A 20226-2026 artfynd.xlsx
+++ b/artfynd/A 20226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95030595</v>
+        <v>95030623</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380391.3282861934</v>
+        <v>380247</v>
       </c>
       <c r="R2" t="n">
-        <v>6751976.453756285</v>
+        <v>6751738</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95030646</v>
+        <v>95030599</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380368.6739802791</v>
+        <v>380410</v>
       </c>
       <c r="R3" t="n">
-        <v>6751955.778495458</v>
+        <v>6751980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95030623</v>
+        <v>95030613</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380247.1784884178</v>
+        <v>380356</v>
       </c>
       <c r="R4" t="n">
-        <v>6751738.66763288</v>
+        <v>6751923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95030599</v>
+        <v>95030595</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380410.0141583089</v>
+        <v>380391</v>
       </c>
       <c r="R5" t="n">
-        <v>6751980.697608667</v>
+        <v>6751976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95030620</v>
+        <v>95030597</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380402.6767426534</v>
+        <v>380320</v>
       </c>
       <c r="R6" t="n">
-        <v>6752009.201830065</v>
+        <v>6751860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95030613</v>
+        <v>95030600</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380355.862750204</v>
+        <v>380370</v>
       </c>
       <c r="R7" t="n">
-        <v>6751923.07919493</v>
+        <v>6751947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95030597</v>
+        <v>95030620</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380319.5976840205</v>
+        <v>380403</v>
       </c>
       <c r="R8" t="n">
-        <v>6751860.473859572</v>
+        <v>6752009</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95030643</v>
+        <v>95030642</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380311.7821994899</v>
+        <v>380372</v>
       </c>
       <c r="R9" t="n">
-        <v>6751860.249550073</v>
+        <v>6751954</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95030600</v>
+        <v>95030643</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380369.8417227904</v>
+        <v>380312</v>
       </c>
       <c r="R10" t="n">
-        <v>6751946.969525224</v>
+        <v>6751860</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95030642</v>
+        <v>95030646</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380372.5243408239</v>
+        <v>380368</v>
       </c>
       <c r="R11" t="n">
-        <v>6751954.187410179</v>
+        <v>6751956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,6 +1642,103 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95030635</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dundern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>380429</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6752027</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20226-2026 artfynd.xlsx
+++ b/artfynd/A 20226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030623</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030597</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030600</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030642</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030643</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030646</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030635</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>